--- a/Magistrale/Tesi/selezione-progetti.xlsx
+++ b/Magistrale/Tesi/selezione-progetti.xlsx
@@ -555,7 +555,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
   </cols>
@@ -775,7 +775,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Traccia gia' aperta e unico candidato con codice interamente proprio. L'ingegneria c'e' (circa 130k righe di Go); manca la parte scientifica: valutazione su collezioni standard (BEIR, MS MARCO), curve recall@k contro latenza, confronto con Meilisearch, Tantivy ed Elasticsearch e soprattutto uno studio sulla fusione lessicale piu' densa (RRF contro pesatura), che e' il candidato piu' forte a diventare la domanda di tesi.</t>
+          <t>Traccia gia' aperta e unico candidato con codice interamente proprio. L'ingegneria c'e' (2.850 righe di codice piu' 2.060 di test); manca la parte scientifica: valutazione su collezioni standard (BEIR, MS MARCO), curve recall@k contro latenza, confronto con Meilisearch, Tantivy ed Elasticsearch e soprattutto uno studio sulla fusione lessicale piu' densa (RRF contro pesatura), che e' il candidato piu' forte a diventare la domanda di tesi.</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
@@ -2726,7 +2726,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M383"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Traccia gia' aperta e unico candidato con codice interamente proprio. L'ingegneria c'e' (circa 130k righe di Go); manca la parte scientifica: valutazione su collezioni standard (BEIR, MS MARCO), curve recall@k contro latenza, confronto con Meilisearch, Tantivy ed Elasticsearch e soprattutto uno studio sulla fusione lessicale piu' densa (RRF contro pesatura), che e' il candidato piu' forte a diventare la domanda di tesi.</t>
+          <t>Traccia gia' aperta e unico candidato con codice interamente proprio. L'ingegneria c'e' (2.850 righe di codice piu' 2.060 di test); manca la parte scientifica: valutazione su collezioni standard (BEIR, MS MARCO), curve recall@k contro latenza, confronto con Meilisearch, Tantivy ed Elasticsearch e soprattutto uno studio sulla fusione lessicale piu' densa (RRF contro pesatura), che e' il candidato piu' forte a diventare la domanda di tesi.</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
